--- a/02_加值成品/九下/九下1-2_三種難度測驗卷.xlsx
+++ b/02_加值成品/九下/九下1-2_三種難度測驗卷.xlsx
@@ -490,19 +490,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國三下學期 九下1-2 電流的熱效應　測驗　★☆☆ 基礎（記憶・理解）</t>
+          <t>國三下學期 九下1-2 電流的熱效應　測驗　★☆☆ 基礎（記憶・理解）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -519,16 +523,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -537,18 +561,38 @@
           <t>電流通過導體產生熱稱？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>光能與熱能</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>熱效應</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>電流的熱效應</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>快</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>發熱</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -557,18 +601,38 @@
           <t>電流的熱效應把電能轉為？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>其他能量</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>電流熱效應</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>電流的熱效應</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>熱能</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>轉換</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -577,18 +641,38 @@
           <t>每秒消耗的電能是？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>電流熱效應</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>光能與熱能</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>電功率</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>越快</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>功率</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -597,18 +681,38 @@
           <t>電功率的單位是？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>瓦特(W)</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
+          <t>耗電更快</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>較多</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>熱能</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
           <t>功率</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -617,18 +721,38 @@
           <t>電暖器利用什麼效應？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>電流的熱效應</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>其他能量</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>電功率</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>熱效應</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>發熱</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -637,18 +761,38 @@
           <t>電鍋煮飯利用？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>其他能量</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>熱效應</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>電流的熱效應</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>越快</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>加熱</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -657,18 +801,38 @@
           <t>電器標示的瓦數是？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>電流的熱效應</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>電功率</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>瓦特(W)</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>電流熱效應</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>消耗</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -677,18 +841,38 @@
           <t>電流做功把電能轉成？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>其他能量</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
+          <t>電能轉熱能</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>快</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>熱能</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
           <t>轉換</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -697,18 +881,38 @@
           <t>電流通過導體發熱是哪種效應？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>熱效應</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
+          <t>越快</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>熱能</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>瓦特(W)</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
           <t>發熱</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -717,12 +921,32 @@
           <t>使用電器的時間越長耗電量？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>越快</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>電功率</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>熱效應</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>越多</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>耗電</t>
         </is>
@@ -730,7 +954,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -742,19 +966,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國三下學期 九下1-2 電流的熱效應　測驗　★★☆ 進階（應用・分析）</t>
+          <t>國三下學期 九下1-2 電流的熱效應　測驗　★★☆ 進階（應用・分析）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -771,16 +999,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -789,18 +1037,38 @@
           <t>功率越大的電器耗電？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>熱效應</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>電功率</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>電流的熱效應</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>越快</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>耗能</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -809,18 +1077,38 @@
           <t>電熱水器主要能量轉換？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>快</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>熱能</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>電流的熱效應</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>電能轉熱能</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>熱效應</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -829,18 +1117,38 @@
           <t>電燈把電能轉成？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>電功率</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>電流的熱效應</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>光能與熱能</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>電能轉熱能</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>轉換</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -849,18 +1157,38 @@
           <t>電功率標示100W比60W？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>越多</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>耗電更快</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>快</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>其他能量</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>功率大</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -869,18 +1197,38 @@
           <t>熱效應與電阻常有何關係？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>100W耗電快通常較亮</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>電阻大處常發熱明顯</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>用低功率或減少使用時間</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>總用電過大可能過載</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>電阻</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -889,18 +1237,38 @@
           <t>電能的計費依據約為？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>電流過大發熱過度</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>用電功率與時間</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>相同時間耗電較少</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>用低功率或減少使用時間</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>電費</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -909,18 +1277,38 @@
           <t>吹風機發熱靠？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>電流熱效應</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
+          <t>越多</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>其他能量</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>熱能</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
           <t>發熱</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -929,18 +1317,38 @@
           <t>相同時間下大功率電器耗電？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>瓦特(W)</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>熱效應</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>較多</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>電功率</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>功率</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -949,18 +1357,38 @@
           <t>電熨斗發熱利用電流的？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>熱效應</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
+          <t>熱能</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>電流的熱效應</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>快</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
           <t>發熱</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -969,12 +1397,32 @@
           <t>功率100W的電器比60W耗電？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>耗電更快</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>熱效應</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>電流的熱效應</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>快</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>功率</t>
         </is>
@@ -982,7 +1430,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -994,19 +1442,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國三下學期 九下1-2 電流的熱效應　測驗　★★★ 挑戰（評鑑・創造）</t>
+          <t>國三下學期 九下1-2 電流的熱效應　測驗　★★★ 挑戰（評鑑・創造）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -1023,16 +1475,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -1041,18 +1513,38 @@
           <t>為何電熱器要用高電阻的發熱線？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>100W耗電快通常較亮</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>移高中,國中重概念應用</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>相同時間耗電較少</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>電阻大處電流通過發熱明顯</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>熱效應</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -1061,18 +1553,38 @@
           <t>如何從功率與使用時間概念省電？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>電流做功可驅動不同裝置轉換能量</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>100W耗電快通常較亮</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>電阻大處常發熱明顯</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>用低功率或減少使用時間</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>省電</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -1081,18 +1593,38 @@
           <t>電能為何能轉成多種形式？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>電流做功可驅動不同裝置轉換能量</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>利:電暖器;弊:電線過熱走火</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>用低功率或減少使用時間</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>總用電過大可能過載</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
           <t>轉換</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -1101,18 +1633,38 @@
           <t>比較100W與60W燈泡耗電與亮度？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>電阻大處電流通過發熱明顯</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>電阻大處常發熱明顯</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>移高中,國中重概念應用</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>100W耗電快通常較亮</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>功率</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -1121,18 +1673,38 @@
           <t>電流熱效應有利也有弊各舉例？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>利:電暖器;弊:電線過熱走火</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
+          <t>電流過大發熱過度</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>用低功率或減少使用時間</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>耗電=功率×時間</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
           <t>雙面</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -1141,18 +1713,38 @@
           <t>長時間高功率電器同時使用風險？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>總用電過大可能過載</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
+          <t>用低功率或減少使用時間</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>100W耗電快通常較亮</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>電流做功可驅動不同裝置轉換能量</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
           <t>安全</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -1161,18 +1753,38 @@
           <t>電費與電功率時間關係(概念)？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>移高中,國中重概念應用</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>100W耗電快通常較亮</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>耗電=功率×時間</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>相同時間耗電較少</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>計費</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -1181,18 +1793,38 @@
           <t>為何課綱不涉電功率公式計算？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>用低功率或減少使用時間</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>100W耗電快通常較亮</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>移高中,國中重概念應用</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>用電功率與時間</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>課綱</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -1201,18 +1833,38 @@
           <t>為何電線過載可能引起火災？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>電阻大處電流通過發熱明顯</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>相同時間耗電較少</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>用低功率或減少使用時間</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>電流過大發熱過度</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>熱效應</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -1221,12 +1873,32 @@
           <t>如何用低功率電器達到省電？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>100W耗電快通常較亮</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>電阻大處電流通過發熱明顯</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>相同時間耗電較少</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>耗電=功率×時間</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>省電</t>
         </is>
@@ -1234,7 +1906,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/02_加值成品/九下/九下1-2_三種難度測驗卷.xlsx
+++ b/02_加值成品/九下/九下1-2_三種難度測驗卷.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>發熱</t>
+          <t>發熱：電流通過導體時會使導體溫度升高，這種現象叫做電流的熱效應</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>轉換</t>
+          <t>轉換：熱效應就是電流做功，把原本的電能轉換成熱能釋放出來</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>功率</t>
+          <t>功率：電功率表示電器每秒鐘所消耗的電能多寡，數字越大表示越耗電</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>功率</t>
+          <t>功率：電功率的單位是瓦特，寫成W，是用來標示電器耗電快慢的單位</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>發熱</t>
+          <t>發熱：電暖器是利用電流通過發熱線產生熱，靠的就是電流的熱效應</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>加熱</t>
+          <t>加熱：電鍋是利用電流通過發熱元件產生熱量，把電能轉成熱能來煮熟食物</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>消耗</t>
+          <t>消耗：電器上標示的瓦數就是它的電功率，代表每秒消耗多少電能</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>轉換</t>
+          <t>轉換：電流通過電器做功時，會把電能轉換成熱能、光能等各種形式的能量</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>發熱</t>
+          <t>發熱：電流通過導體使溫度升高的現象，稱為電流的熱效應</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>耗電</t>
+          <t>耗電：電器使用的時間越久，累積消耗的電能就越多</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>耗能</t>
+          <t>耗能：電功率越大代表每秒消耗的電能越多，所以耗電速度也越快</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>熱效應</t>
+          <t>熱效應：電熱水器是利用電流的熱效應，把電能轉換成熱能加熱水</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>轉換</t>
+          <t>轉換：電燈通電後會發光也會發熱，代表電能同時轉換成了光能和熱能</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>功率大</t>
+          <t>功率大：瓦數越大代表電功率越大，相同時間內消耗的電能就越多，耗電更快</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>電阻</t>
+          <t>電阻：電流通過電阻較大的地方時，比較容易產生明顯的發熱現象</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>電費</t>
+          <t>電費：電費是依照電器的功率大小，乘上使用的時間長短來計算的</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>發熱</t>
+          <t>發熱：吹風機裡的發熱線通電後會發熱，這正是利用電流的熱效應</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>功率</t>
+          <t>功率：在使用時間相同的情況下，功率越大的電器消耗的電能就越多</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>發熱</t>
+          <t>發熱：電熨斗內部的發熱線通電後升溫，正是利用電流的熱效應</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>功率</t>
+          <t>功率：瓦數越大代表電功率越大，相同時間內消耗的電能也越多，耗電較快</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>熱效應</t>
+          <t>熱效應：電阻越大的地方，電流通過時越容易產生明顯的熱，所以發熱線要用高電阻材料</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>省電</t>
+          <t>省電：選用功率較小的電器，或縮短電器使用的時間，都能減少消耗的電能</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>轉換</t>
+          <t>轉換：電流通過不同裝置時會做不同的功，所以電能能轉換成熱能、光能、動能等多種形式</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>功率</t>
+          <t>功率：功率較大的100W燈泡每秒消耗的電能較多，通常也會比60W燈泡亮</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>雙面</t>
+          <t>雙面：熱效應有好處也有壞處，好處如電暖器取暖，壞處是電線過熱可能引發火災</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>安全</t>
+          <t>安全：多個高功率電器同時使用會讓總電流變得很大，容易造成電路過載發生危險</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>計費</t>
+          <t>計費：消耗的電能等於電功率乘上使用的時間，這是計算電費的基本概念</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>課綱</t>
+          <t>課綱：詳細的公式計算留到高中再學，國中階段重點是理解概念和生活中的應用</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>熱效應</t>
+          <t>熱效應：電線通過的電流太大時，因熱效應產生的熱量過多，可能使電線過熱進而走火</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>省電</t>
+          <t>省電：功率較低的電器在相同使用時間下，消耗的電能比較少，能達到省電效果</t>
         </is>
       </c>
     </row>

--- a/02_加值成品/九下/九下1-2_三種難度測驗卷.xlsx
+++ b/02_加值成品/九下/九下1-2_三種難度測驗卷.xlsx
@@ -563,12 +563,12 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>光能與熱能</t>
+          <t>耗電更快</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>熱效應</t>
+          <t>越多</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
@@ -578,7 +578,7 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>快</t>
+          <t>其他能量</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
@@ -608,12 +608,12 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
+          <t>瓦特(W)</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
           <t>電流熱效應</t>
-        </is>
-      </c>
-      <c r="E4" s="7" t="inlineStr">
-        <is>
-          <t>電流的熱效應</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
@@ -723,17 +723,17 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>電流的熱效應</t>
+          <t>耗電更快</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
+          <t>瓦特(W)</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
           <t>其他能量</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>電功率</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -763,7 +763,7 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>其他能量</t>
+          <t>瓦特(W)</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
@@ -773,12 +773,12 @@
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>電流的熱效應</t>
+          <t>電能轉熱能</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>越快</t>
+          <t>較多</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
@@ -888,17 +888,17 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>越快</t>
+          <t>光能與熱能</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>熱能</t>
+          <t>耗電更快</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>瓦特(W)</t>
+          <t>電功率</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
@@ -1039,17 +1039,17 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>熱效應</t>
+          <t>耗電更快</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>電功率</t>
+          <t>光能與熱能</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>電流的熱效應</t>
+          <t>瓦特(W)</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -1079,17 +1079,17 @@
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>快</t>
+          <t>越多</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>熱能</t>
+          <t>熱效應</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>電流的熱效應</t>
+          <t>電功率</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>電功率</t>
+          <t>較多</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>電流的熱效應</t>
+          <t>其他能量</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>電能轉熱能</t>
+          <t>瓦特(W)</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
@@ -1159,22 +1159,22 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
+          <t>光能與熱能</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>耗電更快</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>電流熱效應</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
           <t>越多</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>耗電更快</t>
-        </is>
-      </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>快</t>
-        </is>
-      </c>
-      <c r="F6" s="7" t="inlineStr">
-        <is>
-          <t>其他能量</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
@@ -1284,17 +1284,17 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>越多</t>
+          <t>電流的熱效應</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
+          <t>熱能</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
           <t>其他能量</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>熱能</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>熱能</t>
+          <t>電能轉熱能</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>電流的熱效應</t>
+          <t>其他能量</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>快</t>
+          <t>光能與熱能</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
@@ -1399,17 +1399,17 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>耗電更快</t>
+          <t>電流的熱效應</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>熱效應</t>
+          <t>較多</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>電流的熱效應</t>
+          <t>越多</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
